--- a/data/quotas/quota_onnuri_2026_풍납시장_온누리가맹점_조사쿼터_1791809776794.xlsx
+++ b/data/quotas/quota_onnuri_2026_풍납시장_온누리가맹점_조사쿼터_1791809776794.xlsx
@@ -397,21 +397,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:O11"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="11.83203125" customWidth="1"/>
     <col min="3" max="3" width="42.83203125" customWidth="1"/>
     <col min="4" max="4" width="20.83203125" customWidth="1"/>
     <col min="5" max="5" width="12.6328125" customWidth="1"/>
-    <col min="6" max="6" width="46.83203125" customWidth="1"/>
-    <col min="7" max="7" width="14.83203125" customWidth="1"/>
-    <col min="8" max="8" width="39.83203125" customWidth="1"/>
-    <col min="9" max="9" width="17.03515625" customWidth="1"/>
-    <col min="10" max="10" width="14.83203125" customWidth="1"/>
+    <col min="6" max="6" width="10.83203125" customWidth="1"/>
+    <col min="7" max="7" width="10.83203125" customWidth="1"/>
+    <col min="8" max="8" width="46.83203125" customWidth="1"/>
+    <col min="9" max="9" width="14.83203125" customWidth="1"/>
+    <col min="10" max="10" width="39.83203125" customWidth="1"/>
     <col min="11" max="11" width="17.03515625" customWidth="1"/>
     <col min="12" max="12" width="14.83203125" customWidth="1"/>
-    <col min="13" max="13" width="12.6328125" customWidth="1"/>
+    <col min="13" max="13" width="17.03515625" customWidth="1"/>
+    <col min="14" max="14" width="14.83203125" customWidth="1"/>
+    <col min="15" max="15" width="12.6328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -431,27 +433,33 @@
         <v>대표자명</v>
       </c>
       <c r="F1" t="str">
+        <v>성별</v>
+      </c>
+      <c r="G1" t="str">
+        <v>나이</v>
+      </c>
+      <c r="H1" t="str">
         <v>주소</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>온누리업종</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>마켓비즈산업분류</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>개업/설립일</v>
       </c>
-      <c r="J1" t="str">
+      <c r="L1" t="str">
         <v>온누리지류</v>
       </c>
-      <c r="K1" t="str">
+      <c r="M1" t="str">
         <v>온누리디지털</v>
       </c>
-      <c r="L1" t="str">
+      <c r="N1" t="str">
         <v>전화번호</v>
       </c>
-      <c r="M1" t="str">
+      <c r="O1" t="str">
         <v>가맹상태</v>
       </c>
     </row>
@@ -472,27 +480,33 @@
         <v>연락처</v>
       </c>
       <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
+        <v/>
+      </c>
+      <c r="H2" t="str">
         <v>서울특별시 송파구 풍납동   1층</v>
       </c>
-      <c r="G2" t="str">
+      <c r="I2" t="str">
         <v>수산물</v>
       </c>
-      <c r="H2" t="str">
+      <c r="J2" t="str">
         <v>신선</v>
       </c>
-      <c r="I2" t="str">
+      <c r="K2" t="str">
         <v>2020.10.06</v>
       </c>
-      <c r="J2" t="str">
-        <v>Y</v>
-      </c>
-      <c r="K2" t="str">
+      <c r="L2" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M2" t="str">
         <v>N</v>
       </c>
-      <c r="L2" t="str">
+      <c r="N2" t="str">
         <v>02-000-0000</v>
       </c>
-      <c r="M2" t="str">
+      <c r="O2" t="str">
         <v>정상가맹</v>
       </c>
     </row>
@@ -513,27 +527,33 @@
         <v>연락처</v>
       </c>
       <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
         <v>서울특별시 송파구 풍납동 87-4 예작헤어라인</v>
       </c>
-      <c r="G3" t="str">
+      <c r="I3" t="str">
         <v>기타소매업</v>
       </c>
-      <c r="H3" t="str">
+      <c r="J3" t="str">
         <v>두발 미용업</v>
       </c>
-      <c r="I3" t="str">
+      <c r="K3" t="str">
         <v>2012.03.13</v>
       </c>
-      <c r="J3" t="str">
-        <v>Y</v>
-      </c>
-      <c r="K3" t="str">
-        <v>Y</v>
-      </c>
       <c r="L3" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M3" t="str">
+        <v>Y</v>
+      </c>
+      <c r="N3" t="str">
         <v>02-000-0000</v>
       </c>
-      <c r="M3" t="str">
+      <c r="O3" t="str">
         <v>정상가맹</v>
       </c>
     </row>
@@ -554,27 +574,33 @@
         <v>연락처</v>
       </c>
       <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
         <v>서울특별시 송파구 풍납동 2층 201호</v>
       </c>
-      <c r="G4" t="str">
+      <c r="I4" t="str">
         <v>기타소매업</v>
       </c>
-      <c r="H4" t="str">
+      <c r="J4" t="str">
         <v>피부 미용업</v>
       </c>
-      <c r="I4" t="str">
+      <c r="K4" t="str">
         <v>2023.10.06</v>
       </c>
-      <c r="J4" t="str">
-        <v>Y</v>
-      </c>
-      <c r="K4" t="str">
+      <c r="L4" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M4" t="str">
         <v>N</v>
       </c>
-      <c r="L4" t="str">
+      <c r="N4" t="str">
         <v>02-000-0000</v>
       </c>
-      <c r="M4" t="str">
+      <c r="O4" t="str">
         <v>정상가맹</v>
       </c>
     </row>
@@ -595,27 +621,33 @@
         <v>연락처</v>
       </c>
       <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
         <v>서울특별시 송파구 풍납동 1층 4호</v>
       </c>
-      <c r="G5" t="str">
+      <c r="I5" t="str">
         <v>농산물</v>
       </c>
-      <c r="H5" t="str">
+      <c r="J5" t="str">
         <v>곡물</v>
       </c>
-      <c r="I5" t="str">
+      <c r="K5" t="str">
         <v>2025.06.11</v>
       </c>
-      <c r="J5" t="str">
-        <v>Y</v>
-      </c>
-      <c r="K5" t="str">
-        <v>Y</v>
-      </c>
       <c r="L5" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M5" t="str">
+        <v>Y</v>
+      </c>
+      <c r="N5" t="str">
         <v>02-000-0000</v>
       </c>
-      <c r="M5" t="str">
+      <c r="O5" t="str">
         <v>정상가맹</v>
       </c>
     </row>
@@ -636,27 +668,33 @@
         <v>연락처</v>
       </c>
       <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
         <v>서울특별시 송파구 풍납동 149-12 1층</v>
       </c>
-      <c r="G6" t="str">
+      <c r="I6" t="str">
         <v>수산물</v>
       </c>
-      <c r="H6" t="str">
+      <c r="J6" t="str">
         <v>음ㆍ식료품 및 담배 도매업 외 1개</v>
       </c>
-      <c r="I6" t="str">
+      <c r="K6" t="str">
         <v>2022.03.14</v>
       </c>
-      <c r="J6" t="str">
-        <v>Y</v>
-      </c>
-      <c r="K6" t="str">
-        <v>Y</v>
-      </c>
       <c r="L6" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M6" t="str">
+        <v>Y</v>
+      </c>
+      <c r="N6" t="str">
         <v>02-000-0000</v>
       </c>
-      <c r="M6" t="str">
+      <c r="O6" t="str">
         <v>정상가맹</v>
       </c>
     </row>
@@ -677,27 +715,33 @@
         <v>대표자</v>
       </c>
       <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
         <v>서울특별시 송파구 풍납동   1층</v>
       </c>
-      <c r="G7" t="str">
+      <c r="I7" t="str">
         <v>가공식품</v>
       </c>
-      <c r="H7" t="str">
+      <c r="J7" t="str">
         <v>가공식품</v>
       </c>
-      <c r="I7" t="str">
+      <c r="K7" t="str">
         <v>2011-05-12</v>
       </c>
-      <c r="J7" t="str">
-        <v>Y</v>
-      </c>
-      <c r="K7" t="str">
+      <c r="L7" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M7" t="str">
         <v>N</v>
       </c>
-      <c r="L7" t="str">
+      <c r="N7" t="str">
         <v>02-000-0000</v>
       </c>
-      <c r="M7" t="str">
+      <c r="O7" t="str">
         <v>정상가맹</v>
       </c>
     </row>
@@ -718,27 +762,33 @@
         <v>연락처</v>
       </c>
       <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
         <v>서울특별시 송파구 풍납동 1층</v>
       </c>
-      <c r="G8" t="str">
+      <c r="I8" t="str">
         <v>농산물</v>
       </c>
-      <c r="H8" t="str">
+      <c r="J8" t="str">
         <v>육류 소매업</v>
       </c>
-      <c r="I8" t="str">
+      <c r="K8" t="str">
         <v>2014.01.20</v>
       </c>
-      <c r="J8" t="str">
-        <v>Y</v>
-      </c>
-      <c r="K8" t="str">
-        <v>Y</v>
-      </c>
       <c r="L8" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M8" t="str">
+        <v>Y</v>
+      </c>
+      <c r="N8" t="str">
         <v>02-000-0000</v>
       </c>
-      <c r="M8" t="str">
+      <c r="O8" t="str">
         <v>정상가맹</v>
       </c>
     </row>
@@ -759,27 +809,33 @@
         <v>연락처</v>
       </c>
       <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
         <v>서울특별시 송파구 풍납동   1층</v>
       </c>
-      <c r="G9" t="str">
+      <c r="I9" t="str">
         <v>농산물</v>
       </c>
-      <c r="H9" t="str">
+      <c r="J9" t="str">
         <v>통신ㆍ방송장비 및 부품 도매업 외 1개</v>
       </c>
-      <c r="I9" t="str">
+      <c r="K9" t="str">
         <v>1991.04.03</v>
       </c>
-      <c r="J9" t="str">
-        <v>Y</v>
-      </c>
-      <c r="K9" t="str">
-        <v>Y</v>
-      </c>
       <c r="L9" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M9" t="str">
+        <v>Y</v>
+      </c>
+      <c r="N9" t="str">
         <v>02-000-0000</v>
       </c>
-      <c r="M9" t="str">
+      <c r="O9" t="str">
         <v>정상가맹</v>
       </c>
     </row>
@@ -800,27 +856,33 @@
         <v>연락처</v>
       </c>
       <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
         <v>서울특별시 송파구 풍납동 477-3 1층</v>
       </c>
-      <c r="G10" t="str">
+      <c r="I10" t="str">
         <v>기타소매업</v>
       </c>
-      <c r="H10" t="str">
+      <c r="J10" t="str">
         <v>음ㆍ식료품 및 담배 도매업 외 1개</v>
       </c>
-      <c r="I10" t="str">
+      <c r="K10" t="str">
         <v>2016.12.15</v>
       </c>
-      <c r="J10" t="str">
-        <v>Y</v>
-      </c>
-      <c r="K10" t="str">
-        <v>Y</v>
-      </c>
       <c r="L10" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M10" t="str">
+        <v>Y</v>
+      </c>
+      <c r="N10" t="str">
         <v>02-000-0000</v>
       </c>
-      <c r="M10" t="str">
+      <c r="O10" t="str">
         <v>정상가맹</v>
       </c>
     </row>
@@ -841,33 +903,39 @@
         <v>연락처</v>
       </c>
       <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
         <v>서울특별시 송파구 풍납동 478 1층 독도쭈꾸미</v>
       </c>
-      <c r="G11" t="str">
+      <c r="I11" t="str">
         <v>음식점업</v>
       </c>
-      <c r="H11" t="str">
+      <c r="J11" t="str">
         <v>한식 일반 음식점업 외 1개</v>
       </c>
-      <c r="I11" t="str">
+      <c r="K11" t="str">
         <v>2010.06.16</v>
       </c>
-      <c r="J11" t="str">
-        <v>Y</v>
-      </c>
-      <c r="K11" t="str">
-        <v>Y</v>
-      </c>
       <c r="L11" t="str">
+        <v>Y</v>
+      </c>
+      <c r="M11" t="str">
+        <v>Y</v>
+      </c>
+      <c r="N11" t="str">
         <v>02-000-0000</v>
       </c>
-      <c r="M11" t="str">
+      <c r="O11" t="str">
         <v>정상가맹</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O11"/>
   </ignoredErrors>
 </worksheet>
 </file>